--- a/majURLCanonical/ig/StructureDefinition-fr-cda-clinical-document-ips.xlsx
+++ b/majURLCanonical/ig/StructureDefinition-fr-cda-clinical-document-ips.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-29T14:19:09+00:00</t>
+    <t>2026-09-30T08:05:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
